--- a/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,16 +37,25 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>صابون ريفولى - 110 جم</t>
-  </si>
-  <si>
-    <t>حفاضات جود كير مقاس 5 - 40 حفاضة</t>
-  </si>
-  <si>
-    <t>حلوانى مربى مشمش- 700 جم</t>
-  </si>
-  <si>
-    <t>شامبو وبسلم سباركل للشعر العادي - 350 مل</t>
+    <t>بيبسى - 2.43 لتر</t>
+  </si>
+  <si>
+    <t>مناديل فاميليا تواليت مضغوط 5 رول + 1 رول هدية - 6 رول</t>
+  </si>
+  <si>
+    <t>مكرونة شعرية كايرو - 400 جم</t>
+  </si>
+  <si>
+    <t>مكرونة كايرو مرمرية - 400 جم</t>
+  </si>
+  <si>
+    <t>جبنة لا فاش كيرى كلاسيك - 8 مثلث</t>
+  </si>
+  <si>
+    <t>كوكا كولا كانز ستار - 320 مل</t>
+  </si>
+  <si>
+    <t>فرسكا شوكو بار حلاوة12 قطعه حجم اكبر 5 جنية</t>
   </si>
   <si>
     <t>YES</t>
@@ -407,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -435,121 +444,155 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>1309</v>
+        <v>589</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>534</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>1309</v>
+        <v>3442</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>44.5</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>2424</v>
+        <v>5849</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>865</v>
+        <v>186.25</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>2424</v>
+        <v>5850</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>173</v>
+        <v>186.5</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>2508</v>
+        <v>10149</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>753.75</v>
+        <v>1240</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>6034</v>
+        <v>10149</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>43.25</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>6034</v>
+        <v>11396</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>335</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>12588</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>52.5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>12588</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D8">
-        <v>1038</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="D10">
+        <v>630</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,25 +37,31 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>بيبسى - 2.43 لتر</t>
-  </si>
-  <si>
-    <t>مناديل فاميليا تواليت مضغوط 5 رول + 1 رول هدية - 6 رول</t>
-  </si>
-  <si>
-    <t>مكرونة شعرية كايرو - 400 جم</t>
-  </si>
-  <si>
-    <t>مكرونة كايرو مرمرية - 400 جم</t>
-  </si>
-  <si>
-    <t>جبنة لا فاش كيرى كلاسيك - 8 مثلث</t>
-  </si>
-  <si>
-    <t>كوكا كولا كانز ستار - 320 مل</t>
-  </si>
-  <si>
-    <t>فرسكا شوكو بار حلاوة12 قطعه حجم اكبر 5 جنية</t>
+    <t>كوكا كولا جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>سبرايت جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>فانتا برتقال جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>شويبس جولد خوخ جيب - 240 مل</t>
+  </si>
+  <si>
+    <t>كوكا كولا تربو زيرو - 300 مل</t>
+  </si>
+  <si>
+    <t>أمريكانا فول سادة 20% خصم-( 12عرض*2عبوة ) 400 جم</t>
+  </si>
+  <si>
+    <t>فاين ديل مناديل وجه 380 منديل *2 طبقة عبوة التوفير 380 منديل</t>
+  </si>
+  <si>
+    <t>مشروب بودرة تانج مانجو جديد 2 لتر - 40 جرام</t>
   </si>
   <si>
     <t>YES</t>
@@ -416,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -444,7 +450,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -453,49 +459,49 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>3442</v>
+        <v>616</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>5849</v>
+        <v>624</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>186.25</v>
+        <v>291.75</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>5850</v>
+        <v>2879</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -504,95 +510,129 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>186.5</v>
+        <v>785</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>10149</v>
+        <v>5494</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>1240</v>
+        <v>292</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>10149</v>
+        <v>11454</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>76.75</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>11396</v>
+        <v>13118</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>335</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>12588</v>
+        <v>13118</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>431</v>
       </c>
       <c r="D9">
-        <v>52.5</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>12588</v>
+        <v>13266</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>262.75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24127</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>120.75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24127</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
         <v>1</v>
       </c>
-      <c r="D10">
-        <v>630</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
+      <c r="D12">
+        <v>1207.5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,31 +37,16 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>كوكا كولا جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>سبرايت جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>فانتا برتقال جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>زيت كريستال عباد الشمس 4 زجاجة - 2.2 لتر</t>
-  </si>
-  <si>
-    <t>شويبس جولد خوخ جيب - 240 مل</t>
-  </si>
-  <si>
-    <t>كوكا كولا تربو زيرو - 300 مل</t>
-  </si>
-  <si>
-    <t>أمريكانا فول سادة 20% خصم-( 12عرض*2عبوة ) 400 جم</t>
-  </si>
-  <si>
-    <t>فاين ديل مناديل وجه 380 منديل *2 طبقة عبوة التوفير 380 منديل</t>
-  </si>
-  <si>
-    <t>مشروب بودرة تانج مانجو جديد 2 لتر - 40 جرام</t>
+    <t>ميني كتاكيتو بالشوكولاتة  - 10 ج</t>
+  </si>
+  <si>
+    <t>سلايت زيت عباد الشمس مكرر- 675 مل</t>
+  </si>
+  <si>
+    <t>زيت عافية ذرة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>فانتا تفاح احمر ستار - 320 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -422,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -450,189 +435,87 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>615</v>
+        <v>975</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>290</v>
+        <v>96.5</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>616</v>
+        <v>975</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>290</v>
+        <v>1158</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>624</v>
+        <v>1082</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>291.75</v>
+        <v>709.5</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>2879</v>
+        <v>2538</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>785</v>
+        <v>881</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>5494</v>
+        <v>3671</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>11454</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>76.75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>13118</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>408</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>13118</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>431</v>
-      </c>
-      <c r="D9">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>13266</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>262.75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24127</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <v>120.75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24127</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1207.5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,13 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>الحمد جبنة موتزاريلا البيضاء - 400 جم</t>
-  </si>
-  <si>
-    <t>الحمد جبنة موتزاريلا البيضاء - 1 كجم</t>
-  </si>
-  <si>
-    <t>ريحانة  بقسماط ناعم - 300 جم</t>
+    <t>سمنة حبوبة نباتى صفراء - 300 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,7 +426,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>6395</v>
+        <v>11403</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -441,95 +435,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1325</v>
+        <v>360.5</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>6395</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>53</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>6396</v>
-      </c>
-      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>6396</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1260</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>7673</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>7673</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>360</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
+++ b/Pricing Logic/modules/manual/output_700_chunk_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,7 +37,67 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>نوفي فينجرز شيكولاتة بيضاء - 5 جنية</t>
+    <t>زيت كريستال الممتاز خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال الممتاز خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 900 مل</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>هنادى زيت خليط- 2.1 لتر</t>
+  </si>
+  <si>
+    <t>هدية زيت خليط- 0.7 لتر</t>
+  </si>
+  <si>
+    <t>سلايت زيت عباد الشمس مكرر- 675 مل</t>
+  </si>
+  <si>
+    <t>سلايت زيت عباد الشمس- 2.1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 2.25 لتر</t>
+  </si>
+  <si>
+    <t>زيت ذرة ريحانة بيور - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت كريستال ذرة 4 زجاجة - 2.2 لتر</t>
+  </si>
+  <si>
+    <t>زيت حلوة خليط - 4.5 لتر</t>
+  </si>
+  <si>
+    <t>سندة زيت خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت حبوبة خليط - 1.8 لتر</t>
+  </si>
+  <si>
+    <t>زيت عافية عباد الشمس - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت عافية ذرة - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 1 لتر</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 700 مل</t>
+  </si>
+  <si>
+    <t>زيت ثمرات خليط - 550 مل</t>
   </si>
   <si>
     <t>YES</t>
@@ -398,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -426,7 +486,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21687</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -435,27 +495,350 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>297</v>
+        <v>866</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21687</v>
+        <v>448</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>24.75</v>
+        <v>625</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>823</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>764.5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>856</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>869</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>858</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>605</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>924</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>612</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>1082</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>715</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>1084</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>716</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>1091</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>655</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>1447</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>754.5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>1490</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>604</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>1492</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>860</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>2916</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>955</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>4203</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>640</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>6497</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>855</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>9358</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>554</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>12661</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>387</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>12662</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>475</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>12923</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>855</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>12924</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>600</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>12925</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>490</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
